--- a/artifacts/input/destination_charges.xlsx
+++ b/artifacts/input/destination_charges.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:G254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,11 +459,16 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SUAPE JOBS</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Abidjan, Ivory Coast</t>
+          <t>Itajai (Santa Catarina), Brazil-Abidjan, Ivory Coast</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -484,7 +489,6 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,7 +514,6 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -536,12 +539,11 @@
       <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,7 +553,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Algeciras, Spain</t>
+          <t>Itajai (Santa Catarina), Brazil-Algeciras, Spain</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -562,7 +564,6 @@
       <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,7 +589,6 @@
       <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,12 +614,11 @@
       <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,7 +628,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Altamira (Tamaulipas), Mexico</t>
+          <t>Itajai (Santa Catarina), Brazil-Altamira (Tamaulipas), Mexico</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -640,7 +639,6 @@
       <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -666,7 +664,6 @@
       <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,12 +689,11 @@
       <c r="E10" t="n">
         <v>9</v>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -707,7 +703,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Asuncion, Paraguay</t>
+          <t>Itajai (Santa Catarina), Brazil-Asuncion, Paraguay</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -718,7 +714,6 @@
       <c r="E11" t="n">
         <v>10</v>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -744,7 +739,6 @@
       <c r="E12" t="n">
         <v>11</v>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -770,12 +764,11 @@
       <c r="E13" t="n">
         <v>12</v>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -785,7 +778,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Balboa, Panama</t>
+          <t>Itajai (Santa Catarina), Brazil-Balboa, Panama</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -796,7 +789,6 @@
       <c r="E14" t="n">
         <v>13</v>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -822,7 +814,6 @@
       <c r="E15" t="n">
         <v>14</v>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -848,12 +839,11 @@
       <c r="E16" t="n">
         <v>15</v>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -863,7 +853,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Bar, Montenegro</t>
+          <t>Itajai (Santa Catarina), Brazil-Bar, Montenegro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -874,7 +864,6 @@
       <c r="E17" t="n">
         <v>16</v>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -900,7 +889,6 @@
       <c r="E18" t="n">
         <v>17</v>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -926,12 +914,11 @@
       <c r="E19" t="n">
         <v>18</v>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -941,7 +928,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Barcelona, Spain</t>
+          <t>Itajai (Santa Catarina), Brazil-Barcelona, Spain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -952,7 +939,6 @@
       <c r="E20" t="n">
         <v>19</v>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -978,7 +964,6 @@
       <c r="E21" t="n">
         <v>20</v>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1004,12 +989,11 @@
       <c r="E22" t="n">
         <v>21</v>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1019,7 +1003,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Basseterre, St Kitts-Nevis</t>
+          <t>Itajai (Santa Catarina), Brazil-Basseterre, St Kitts-Nevis</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1033,6 +1017,9 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1061,6 +1048,9 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1089,11 +1079,14 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1103,7 +1096,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Beira, Mozambique</t>
+          <t>Itajai (Santa Catarina), Brazil-Beira, Mozambique</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1114,7 +1107,6 @@
       <c r="E26" t="n">
         <v>25</v>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1140,7 +1132,6 @@
       <c r="E27" t="n">
         <v>26</v>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1166,12 +1157,11 @@
       <c r="E28" t="n">
         <v>27</v>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1181,7 +1171,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Bridgetown, Barbados</t>
+          <t>Itajai (Santa Catarina), Brazil-Bridgetown, Barbados</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1192,7 +1182,9 @@
       <c r="E29" t="n">
         <v>28</v>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1218,7 +1210,9 @@
       <c r="E30" t="n">
         <v>29</v>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1244,12 +1238,14 @@
       <c r="E31" t="n">
         <v>30</v>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1259,7 +1255,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Buenos Aires (Buenos Aires), Argentina</t>
+          <t>Itajai (Santa Catarina), Brazil-Buenos Aires (Buenos Aires), Argentina</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1270,7 +1266,6 @@
       <c r="E32" t="n">
         <v>31</v>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1296,7 +1291,6 @@
       <c r="E33" t="n">
         <v>32</v>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1322,12 +1316,11 @@
       <c r="E34" t="n">
         <v>33</v>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1337,7 +1330,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Callao, Peru</t>
+          <t>Itajai (Santa Catarina), Brazil-Callao, Peru</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1348,7 +1341,6 @@
       <c r="E35" t="n">
         <v>34</v>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1374,7 +1366,6 @@
       <c r="E36" t="n">
         <v>35</v>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1400,12 +1391,11 @@
       <c r="E37" t="n">
         <v>36</v>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1415,7 +1405,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Campden Park, Saint Vincent and the Grenadines</t>
+          <t>Itajai (Santa Catarina), Brazil-Campden Park, Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1426,7 +1416,9 @@
       <c r="E38" t="n">
         <v>37</v>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1452,7 +1444,9 @@
       <c r="E39" t="n">
         <v>38</v>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1478,12 +1472,14 @@
       <c r="E40" t="n">
         <v>39</v>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1493,7 +1489,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Cap Haitien, Haiti</t>
+          <t>Itajai (Santa Catarina), Brazil-Cap Haitien, Haiti</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1504,7 +1500,6 @@
       <c r="E41" t="n">
         <v>40</v>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1530,7 +1525,6 @@
       <c r="E42" t="n">
         <v>41</v>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1556,12 +1550,11 @@
       <c r="E43" t="n">
         <v>42</v>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1571,7 +1564,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Cape Town (Western Cape), South Africa</t>
+          <t>Itajai (Santa Catarina), Brazil-Cape Town (Western Cape), South Africa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1582,7 +1575,6 @@
       <c r="E44" t="n">
         <v>43</v>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1608,7 +1600,6 @@
       <c r="E45" t="n">
         <v>44</v>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1634,12 +1625,11 @@
       <c r="E46" t="n">
         <v>45</v>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1649,7 +1639,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Cartagena (Bolivar), Colombia</t>
+          <t>Itajai (Santa Catarina), Brazil-Cartagena (Bolivar), Colombia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1660,7 +1650,6 @@
       <c r="E47" t="n">
         <v>46</v>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1686,7 +1675,6 @@
       <c r="E48" t="n">
         <v>47</v>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1712,12 +1700,11 @@
       <c r="E49" t="n">
         <v>48</v>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1727,7 +1714,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Castries (Herault), France</t>
+          <t>Itajai (Santa Catarina), Brazil-Castries (Herault), France</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1738,7 +1725,6 @@
       <c r="E50" t="n">
         <v>49</v>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1764,7 +1750,6 @@
       <c r="E51" t="n">
         <v>50</v>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1790,12 +1775,11 @@
       <c r="E52" t="n">
         <v>51</v>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1805,7 +1789,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Caucedo, Dominican Republic</t>
+          <t>Itajai (Santa Catarina), Brazil-Caucedo, Dominican Republic</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1816,7 +1800,9 @@
       <c r="E53" t="n">
         <v>52</v>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1842,7 +1828,9 @@
       <c r="E54" t="n">
         <v>53</v>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1868,12 +1856,14 @@
       <c r="E55" t="n">
         <v>54</v>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1883,7 +1873,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Charleston (South Carolina), United States</t>
+          <t>Itajai (Santa Catarina), Brazil-Charleston (South Carolina), United States</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1957,7 +1947,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1967,7 +1957,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Charlotte Amalie, Virgin Islands (US)</t>
+          <t>Itajai (Santa Catarina), Brazil-Charlotte Amalie, Virgin Islands (US)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1978,7 +1968,6 @@
       <c r="E59" t="n">
         <v>58</v>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2004,7 +1993,6 @@
       <c r="E60" t="n">
         <v>59</v>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2030,12 +2018,11 @@
       <c r="E61" t="n">
         <v>60</v>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2045,7 +2032,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Constanta (Constanta), Romania</t>
+          <t>Itajai (Santa Catarina), Brazil-Constanta (Constanta), Romania</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2056,7 +2043,6 @@
       <c r="E62" t="n">
         <v>61</v>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2082,7 +2068,6 @@
       <c r="E63" t="n">
         <v>62</v>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2108,12 +2093,11 @@
       <c r="E64" t="n">
         <v>63</v>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2123,7 +2107,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Corinto, Nicaragua</t>
+          <t>Itajai (Santa Catarina), Brazil-Corinto, Nicaragua</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2134,7 +2118,6 @@
       <c r="E65" t="n">
         <v>64</v>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2160,7 +2143,6 @@
       <c r="E66" t="n">
         <v>65</v>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2186,12 +2168,11 @@
       <c r="E67" t="n">
         <v>66</v>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2201,7 +2182,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Cristobal, Panama</t>
+          <t>Itajai (Santa Catarina), Brazil-Cristobal, Panama</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2212,7 +2193,9 @@
       <c r="E68" t="n">
         <v>67</v>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2238,7 +2221,9 @@
       <c r="E69" t="n">
         <v>68</v>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2264,12 +2249,14 @@
       <c r="E70" t="n">
         <v>69</v>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2279,7 +2266,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Dakar, Senegal</t>
+          <t>Itajai (Santa Catarina), Brazil-Dakar, Senegal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2290,7 +2277,6 @@
       <c r="E71" t="n">
         <v>70</v>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2316,7 +2302,6 @@
       <c r="E72" t="n">
         <v>71</v>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2342,12 +2327,11 @@
       <c r="E73" t="n">
         <v>72</v>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2357,7 +2341,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Douala, Cameroon</t>
+          <t>Itajai (Santa Catarina), Brazil-Douala, Cameroon</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2368,7 +2352,6 @@
       <c r="E74" t="n">
         <v>73</v>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2394,7 +2377,6 @@
       <c r="E75" t="n">
         <v>74</v>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2420,12 +2402,11 @@
       <c r="E76" t="n">
         <v>75</v>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2435,7 +2416,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Durban (KwaZulu-Natal), South Africa</t>
+          <t>Itajai (Santa Catarina), Brazil-Durban (KwaZulu-Natal), South Africa</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2446,7 +2427,6 @@
       <c r="E77" t="n">
         <v>76</v>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2472,7 +2452,6 @@
       <c r="E78" t="n">
         <v>77</v>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2498,12 +2477,11 @@
       <c r="E79" t="n">
         <v>78</v>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2513,7 +2491,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Felixstowe, United Kingdom</t>
+          <t>Itajai (Santa Catarina), Brazil-Felixstowe, United Kingdom</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2524,7 +2502,6 @@
       <c r="E80" t="n">
         <v>79</v>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2550,7 +2527,6 @@
       <c r="E81" t="n">
         <v>80</v>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2576,12 +2552,11 @@
       <c r="E82" t="n">
         <v>81</v>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2591,7 +2566,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Freeport, Bahamas</t>
+          <t>Itajai (Santa Catarina), Brazil-Freeport, Bahamas</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2602,7 +2577,9 @@
       <c r="E83" t="n">
         <v>82</v>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2628,7 +2605,9 @@
       <c r="E84" t="n">
         <v>83</v>
       </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2654,12 +2633,14 @@
       <c r="E85" t="n">
         <v>84</v>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2669,7 +2650,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Freetown, Sierra Leone</t>
+          <t>Itajai (Santa Catarina), Brazil-Freetown, Sierra Leone</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2680,7 +2661,6 @@
       <c r="E86" t="n">
         <v>85</v>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2706,7 +2686,6 @@
       <c r="E87" t="n">
         <v>86</v>
       </c>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2732,12 +2711,11 @@
       <c r="E88" t="n">
         <v>87</v>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2747,7 +2725,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Georgetown, Guyana</t>
+          <t>Itajai (Santa Catarina), Brazil-Georgetown, Guyana</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2758,7 +2736,9 @@
       <c r="E89" t="n">
         <v>88</v>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2784,7 +2764,9 @@
       <c r="E90" t="n">
         <v>89</v>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2810,12 +2792,14 @@
       <c r="E91" t="n">
         <v>90</v>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2825,7 +2809,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Guayaquil, Ecuador</t>
+          <t>Itajai (Santa Catarina), Brazil-Guayaquil, Ecuador</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2836,7 +2820,6 @@
       <c r="E92" t="n">
         <v>91</v>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2862,7 +2845,6 @@
       <c r="E93" t="n">
         <v>92</v>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2888,12 +2870,11 @@
       <c r="E94" t="n">
         <v>93</v>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2903,7 +2884,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Houston (Texas), United States</t>
+          <t>Itajai (Santa Catarina), Brazil-Houston (Texas), United States</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2977,7 +2958,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2987,7 +2968,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Kingston, Jamaica</t>
+          <t>Itajai (Santa Catarina), Brazil-Kingston, Jamaica</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2998,7 +2979,9 @@
       <c r="E98" t="n">
         <v>97</v>
       </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3024,7 +3007,9 @@
       <c r="E99" t="n">
         <v>98</v>
       </c>
-      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3050,12 +3035,14 @@
       <c r="E100" t="n">
         <v>99</v>
       </c>
-      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3065,7 +3052,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Kingstown, Saint Vincent and the Grenadines</t>
+          <t>Itajai (Santa Catarina), Brazil-Kingstown, Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3076,7 +3063,6 @@
       <c r="E101" t="n">
         <v>100</v>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3102,7 +3088,6 @@
       <c r="E102" t="n">
         <v>101</v>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3128,12 +3113,11 @@
       <c r="E103" t="n">
         <v>102</v>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3143,7 +3127,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-KRALENDIJK, BONAIRE</t>
+          <t>Itajai (Santa Catarina), Brazil-KRALENDIJK, BONAIRE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3154,7 +3138,9 @@
       <c r="E104" t="n">
         <v>103</v>
       </c>
-      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3180,7 +3166,9 @@
       <c r="E105" t="n">
         <v>104</v>
       </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3206,12 +3194,14 @@
       <c r="E106" t="n">
         <v>105</v>
       </c>
-      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3221,7 +3211,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-La Guaira, Venezuela</t>
+          <t>Itajai (Santa Catarina), Brazil-La Guaira, Venezuela</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3232,7 +3222,6 @@
       <c r="E107" t="n">
         <v>106</v>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3258,7 +3247,6 @@
       <c r="E108" t="n">
         <v>107</v>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3284,7 +3272,6 @@
       <c r="E109" t="n">
         <v>108</v>
       </c>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3310,7 +3297,6 @@
       <c r="E110" t="n">
         <v>109</v>
       </c>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3336,12 +3322,11 @@
       <c r="E111" t="n">
         <v>110</v>
       </c>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3351,7 +3336,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Le Havre (Seine-Maritime), France</t>
+          <t>Itajai (Santa Catarina), Brazil-Le Havre (Seine-Maritime), France</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3362,7 +3347,6 @@
       <c r="E112" t="n">
         <v>111</v>
       </c>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3388,7 +3372,6 @@
       <c r="E113" t="n">
         <v>112</v>
       </c>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3414,12 +3397,11 @@
       <c r="E114" t="n">
         <v>113</v>
       </c>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3429,7 +3411,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Lisbon, Portugal</t>
+          <t>Itajai (Santa Catarina), Brazil-Lisbon, Portugal</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3440,7 +3422,6 @@
       <c r="E115" t="n">
         <v>114</v>
       </c>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3466,7 +3447,6 @@
       <c r="E116" t="n">
         <v>115</v>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3492,12 +3472,11 @@
       <c r="E117" t="n">
         <v>116</v>
       </c>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3507,7 +3486,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-London Gateway, United Kingdom</t>
+          <t>Itajai (Santa Catarina), Brazil-London Gateway, United Kingdom</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3518,7 +3497,6 @@
       <c r="E118" t="n">
         <v>117</v>
       </c>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3544,7 +3522,6 @@
       <c r="E119" t="n">
         <v>118</v>
       </c>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3570,12 +3547,11 @@
       <c r="E120" t="n">
         <v>119</v>
       </c>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3585,7 +3561,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Los Angeles (California), United States</t>
+          <t>Itajai (Santa Catarina), Brazil-Los Angeles (California), United States</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3659,7 +3635,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3669,7 +3645,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Luanda, Angola</t>
+          <t>Itajai (Santa Catarina), Brazil-Luanda, Angola</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3680,7 +3656,6 @@
       <c r="E124" t="n">
         <v>123</v>
       </c>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3706,7 +3681,6 @@
       <c r="E125" t="n">
         <v>124</v>
       </c>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3732,12 +3706,11 @@
       <c r="E126" t="n">
         <v>125</v>
       </c>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3747,7 +3720,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Madrid, Spain</t>
+          <t>Itajai (Santa Catarina), Brazil-Madrid, Spain</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3758,7 +3731,6 @@
       <c r="E127" t="n">
         <v>126</v>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3784,7 +3756,6 @@
       <c r="E128" t="n">
         <v>127</v>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3810,12 +3781,11 @@
       <c r="E129" t="n">
         <v>128</v>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3825,7 +3795,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Malabo, Equatorial Guinea</t>
+          <t>Itajai (Santa Catarina), Brazil-Malabo, Equatorial Guinea</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3836,7 +3806,6 @@
       <c r="E130" t="n">
         <v>129</v>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3862,7 +3831,6 @@
       <c r="E131" t="n">
         <v>130</v>
       </c>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3888,12 +3856,11 @@
       <c r="E132" t="n">
         <v>131</v>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3903,7 +3870,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Maputo, Mozambique</t>
+          <t>Itajai (Santa Catarina), Brazil-Maputo, Mozambique</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3914,7 +3881,6 @@
       <c r="E133" t="n">
         <v>132</v>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3940,7 +3906,6 @@
       <c r="E134" t="n">
         <v>133</v>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3966,12 +3931,11 @@
       <c r="E135" t="n">
         <v>134</v>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3981,7 +3945,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Monrovia, Liberia</t>
+          <t>Itajai (Santa Catarina), Brazil-Monrovia, Liberia</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3992,7 +3956,6 @@
       <c r="E136" t="n">
         <v>135</v>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4018,7 +3981,6 @@
       <c r="E137" t="n">
         <v>136</v>
       </c>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4044,12 +4006,11 @@
       <c r="E138" t="n">
         <v>137</v>
       </c>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4059,7 +4020,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Montevideo, Uruguay</t>
+          <t>Itajai (Santa Catarina), Brazil-Montevideo, Uruguay</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4070,7 +4031,6 @@
       <c r="E139" t="n">
         <v>138</v>
       </c>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4096,7 +4056,6 @@
       <c r="E140" t="n">
         <v>139</v>
       </c>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4122,12 +4081,11 @@
       <c r="E141" t="n">
         <v>140</v>
       </c>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4137,7 +4095,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Nassau, Bahamas</t>
+          <t>Itajai (Santa Catarina), Brazil-Nassau, Bahamas</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4148,7 +4106,9 @@
       <c r="E142" t="n">
         <v>141</v>
       </c>
-      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4174,7 +4134,9 @@
       <c r="E143" t="n">
         <v>142</v>
       </c>
-      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4200,12 +4162,14 @@
       <c r="E144" t="n">
         <v>143</v>
       </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4215,7 +4179,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-New York (New York), United States</t>
+          <t>Itajai (Santa Catarina), Brazil-New York (New York), United States</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4289,7 +4253,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4299,7 +4263,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Oranjestad, Aruba</t>
+          <t>Itajai (Santa Catarina), Brazil-Oranjestad, Aruba</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4310,7 +4274,9 @@
       <c r="E148" t="n">
         <v>147</v>
       </c>
-      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4336,7 +4302,9 @@
       <c r="E149" t="n">
         <v>148</v>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4362,12 +4330,14 @@
       <c r="E150" t="n">
         <v>149</v>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4377,7 +4347,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Paramaribo, Suriname</t>
+          <t>Itajai (Santa Catarina), Brazil-Paramaribo, Suriname</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4388,7 +4358,9 @@
       <c r="E151" t="n">
         <v>150</v>
       </c>
-      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4414,7 +4386,9 @@
       <c r="E152" t="n">
         <v>151</v>
       </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4440,12 +4414,14 @@
       <c r="E153" t="n">
         <v>152</v>
       </c>
-      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4455,7 +4431,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Pointe Noire, Congo</t>
+          <t>Itajai (Santa Catarina), Brazil-Pointe Noire, Congo</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4466,7 +4442,6 @@
       <c r="E154" t="n">
         <v>153</v>
       </c>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4492,7 +4467,6 @@
       <c r="E155" t="n">
         <v>154</v>
       </c>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4518,7 +4492,6 @@
       <c r="E156" t="n">
         <v>155</v>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4544,7 +4517,6 @@
       <c r="E157" t="n">
         <v>156</v>
       </c>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4570,7 +4542,6 @@
       <c r="E158" t="n">
         <v>157</v>
       </c>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4596,12 +4567,11 @@
       <c r="E159" t="n">
         <v>158</v>
       </c>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4611,7 +4581,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Port Everglades (Florida), United States</t>
+          <t>Itajai (Santa Catarina), Brazil-Port Everglades (Florida), United States</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4685,7 +4655,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4695,7 +4665,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Port Louis, Mauritius</t>
+          <t>Itajai (Santa Catarina), Brazil-Port Louis, Mauritius</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4706,7 +4676,6 @@
       <c r="E163" t="n">
         <v>162</v>
       </c>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4732,7 +4701,6 @@
       <c r="E164" t="n">
         <v>163</v>
       </c>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4758,12 +4726,11 @@
       <c r="E165" t="n">
         <v>164</v>
       </c>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4773,7 +4740,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Port of Spain-Trinidad, Trinidad and Tobago</t>
+          <t>Itajai (Santa Catarina), Brazil-Port of Spain-Trinidad, Trinidad and Tobago</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4784,7 +4751,9 @@
       <c r="E166" t="n">
         <v>165</v>
       </c>
-      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4810,7 +4779,9 @@
       <c r="E167" t="n">
         <v>166</v>
       </c>
-      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4836,12 +4807,14 @@
       <c r="E168" t="n">
         <v>167</v>
       </c>
-      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4851,7 +4824,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Port-au-Prince, Haiti</t>
+          <t>Itajai (Santa Catarina), Brazil-Port-au-Prince, Haiti</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4862,7 +4835,6 @@
       <c r="E169" t="n">
         <v>168</v>
       </c>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4888,7 +4860,6 @@
       <c r="E170" t="n">
         <v>169</v>
       </c>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4914,12 +4885,11 @@
       <c r="E171" t="n">
         <v>170</v>
       </c>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4929,7 +4899,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Providenciales, Turks and Caicos</t>
+          <t>Itajai (Santa Catarina), Brazil-Providenciales, Turks and Caicos</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5003,7 +4973,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5013,7 +4983,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Puerto Cabello, Venezuela</t>
+          <t>Itajai (Santa Catarina), Brazil-Puerto Cabello, Venezuela</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5024,7 +4994,6 @@
       <c r="E175" t="n">
         <v>174</v>
       </c>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5050,7 +5019,6 @@
       <c r="E176" t="n">
         <v>175</v>
       </c>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5076,12 +5044,11 @@
       <c r="E177" t="n">
         <v>176</v>
       </c>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5091,7 +5058,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Puerto Cortes, Honduras</t>
+          <t>Itajai (Santa Catarina), Brazil-Puerto Cortes, Honduras</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5102,7 +5069,6 @@
       <c r="E178" t="n">
         <v>177</v>
       </c>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5128,7 +5094,6 @@
       <c r="E179" t="n">
         <v>178</v>
       </c>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5154,12 +5119,11 @@
       <c r="E180" t="n">
         <v>179</v>
       </c>
-      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5169,7 +5133,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Puerto Limon, Costa Rica</t>
+          <t>Itajai (Santa Catarina), Brazil-Puerto Limon, Costa Rica</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5180,7 +5144,6 @@
       <c r="E181" t="n">
         <v>180</v>
       </c>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5206,7 +5169,6 @@
       <c r="E182" t="n">
         <v>181</v>
       </c>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5232,12 +5194,11 @@
       <c r="E183" t="n">
         <v>182</v>
       </c>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5247,7 +5208,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Puerto Moin, Costa Rica</t>
+          <t>Itajai (Santa Catarina), Brazil-Puerto Moin, Costa Rica</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5258,7 +5219,6 @@
       <c r="E184" t="n">
         <v>183</v>
       </c>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5284,7 +5244,6 @@
       <c r="E185" t="n">
         <v>184</v>
       </c>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5310,12 +5269,11 @@
       <c r="E186" t="n">
         <v>185</v>
       </c>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5325,7 +5283,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Puerto Quetzal, Guatemala</t>
+          <t>Itajai (Santa Catarina), Brazil-Puerto Quetzal, Guatemala</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5336,7 +5294,6 @@
       <c r="E187" t="n">
         <v>186</v>
       </c>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5362,7 +5319,6 @@
       <c r="E188" t="n">
         <v>187</v>
       </c>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5388,7 +5344,6 @@
       <c r="E189" t="n">
         <v>188</v>
       </c>
-      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5414,7 +5369,6 @@
       <c r="E190" t="n">
         <v>189</v>
       </c>
-      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5440,7 +5394,6 @@
       <c r="E191" t="n">
         <v>190</v>
       </c>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5466,12 +5419,11 @@
       <c r="E192" t="n">
         <v>191</v>
       </c>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5481,7 +5433,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Road Town, Virgin Islands (Br.)</t>
+          <t>Itajai (Santa Catarina), Brazil-Road Town, Virgin Islands (Br.)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5492,7 +5444,9 @@
       <c r="E193" t="n">
         <v>192</v>
       </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5518,7 +5472,9 @@
       <c r="E194" t="n">
         <v>193</v>
       </c>
-      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5544,12 +5500,14 @@
       <c r="E195" t="n">
         <v>194</v>
       </c>
-      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5559,7 +5517,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Roseau, Dominica</t>
+          <t>Itajai (Santa Catarina), Brazil-Roseau, Dominica</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5573,6 +5531,9 @@
       <c r="F196" t="n">
         <v>1</v>
       </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5601,6 +5562,9 @@
       <c r="F197" t="n">
         <v>1</v>
       </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5629,11 +5593,14 @@
       <c r="F198" t="n">
         <v>1</v>
       </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5643,7 +5610,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Saint George, Grenada</t>
+          <t>Itajai (Santa Catarina), Brazil-Saint George, Grenada</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5654,7 +5621,9 @@
       <c r="E199" t="n">
         <v>198</v>
       </c>
-      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5680,7 +5649,9 @@
       <c r="E200" t="n">
         <v>199</v>
       </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5706,12 +5677,14 @@
       <c r="E201" t="n">
         <v>200</v>
       </c>
-      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5721,7 +5694,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-San Antonio, Chile</t>
+          <t>Itajai (Santa Catarina), Brazil-San Antonio, Chile</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5732,7 +5705,6 @@
       <c r="E202" t="n">
         <v>201</v>
       </c>
-      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5758,7 +5730,6 @@
       <c r="E203" t="n">
         <v>202</v>
       </c>
-      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5784,12 +5755,11 @@
       <c r="E204" t="n">
         <v>203</v>
       </c>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5799,7 +5769,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-San Juan, Puerto Rico</t>
+          <t>Itajai (Santa Catarina), Brazil-San Juan, Puerto Rico</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5810,7 +5780,9 @@
       <c r="E205" t="n">
         <v>204</v>
       </c>
-      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5836,7 +5808,9 @@
       <c r="E206" t="n">
         <v>205</v>
       </c>
-      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5862,7 +5836,9 @@
       <c r="E207" t="n">
         <v>206</v>
       </c>
-      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5888,7 +5864,6 @@
       <c r="E208" t="n">
         <v>207</v>
       </c>
-      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5914,12 +5889,11 @@
       <c r="E209" t="n">
         <v>208</v>
       </c>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5929,7 +5903,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-St Johns, Antigua and Barbuda</t>
+          <t>Itajai (Santa Catarina), Brazil-St Johns, Antigua and Barbuda</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5943,6 +5917,9 @@
       <c r="F210" t="n">
         <v>1</v>
       </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5971,11 +5948,14 @@
       <c r="F211" t="n">
         <v>1</v>
       </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5985,7 +5965,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Tema, Ghana</t>
+          <t>Itajai (Santa Catarina), Brazil-Tema, Ghana</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5996,7 +5976,6 @@
       <c r="E212" t="n">
         <v>211</v>
       </c>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6022,7 +6001,6 @@
       <c r="E213" t="n">
         <v>212</v>
       </c>
-      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6048,7 +6026,6 @@
       <c r="E214" t="n">
         <v>213</v>
       </c>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6074,7 +6051,6 @@
       <c r="E215" t="n">
         <v>214</v>
       </c>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6100,7 +6076,6 @@
       <c r="E216" t="n">
         <v>215</v>
       </c>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6126,12 +6101,11 @@
       <c r="E217" t="n">
         <v>216</v>
       </c>
-      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6141,7 +6115,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Victoria Point, Myanmar</t>
+          <t>Itajai (Santa Catarina), Brazil-Victoria Point, Myanmar</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6152,7 +6126,6 @@
       <c r="E218" t="n">
         <v>217</v>
       </c>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6178,7 +6151,6 @@
       <c r="E219" t="n">
         <v>218</v>
       </c>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6204,12 +6176,11 @@
       <c r="E220" t="n">
         <v>219</v>
       </c>
-      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil</t>
+          <t>Itajai (Santa Catarina), Brazil</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6219,7 +6190,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Navegantes (Santa Catarina), Brazil-Willemstad, Curacao</t>
+          <t>Itajai (Santa Catarina), Brazil-Willemstad, Curacao</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6230,7 +6201,9 @@
       <c r="E221" t="n">
         <v>220</v>
       </c>
-      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6256,7 +6229,9 @@
       <c r="E222" t="n">
         <v>223</v>
       </c>
-      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6282,7 +6257,886 @@
       <c r="E223" t="n">
         <v>224</v>
       </c>
-      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil-Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>225</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil-Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>226</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil-Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>227</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil-Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>228</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil-Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>229</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil-Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>230</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Itajai (Santa Catarina), Brazil-Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>231</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Salvador (Bahia), Brazil-Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>232</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Santos (Sao Paulo), Brazil-Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>233</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Basseterre, St Kitts-Nevis</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Basseterre, St Kitts-Nevis</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>KNBAS</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>234</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Bridgetown, Barbados</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Bridgetown, Barbados</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>BBBGI</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>235</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Campden Park, Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Campden Park, Saint Vincent and the Grenadines</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>VCCRP</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>236</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DOCAU</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>237</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Cristobal, Panama</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Cristobal, Panama</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PACTB</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>238</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Freeport, Bahamas</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Freeport, Bahamas</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>BSFPO</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>239</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Georgetown, Guyana</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Georgetown, Guyana</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>AUGEE</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>240</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Kingston, Jamaica</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Kingston, Jamaica</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>JMKIN</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>241</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>KRALENDIJK, BONAIRE</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-KRALENDIJK, BONAIRE</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>BQKRA</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>242</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Nassau, Bahamas</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Nassau, Bahamas</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>BSNAS</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>243</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Oranjestad, Aruba</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Oranjestad, Aruba</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>AWORJ</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>244</v>
+      </c>
+      <c r="G243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Paramaribo, Suriname</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Paramaribo, Suriname</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SRPBM</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>245</v>
+      </c>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Port of Spain-Trinidad, Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Port of Spain-Trinidad, Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>TTPOS</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>246</v>
+      </c>
+      <c r="G245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Road Town, Virgin Islands (Br.)</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Road Town, Virgin Islands (Br.)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>VGRAD</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>247</v>
+      </c>
+      <c r="G246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Roseau, Dominica</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Roseau, Dominica</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DMRSU</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>248</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Saint George, Grenada</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Saint George, Grenada</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>GDSTG</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>249</v>
+      </c>
+      <c r="G248" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PRSJU</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>250</v>
+      </c>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>St Johns, Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-St Johns, Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>AGSJO</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>251</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Willemstad, Curacao</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Willemstad, Curacao</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ANWIL</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>252</v>
+      </c>
+      <c r="G251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Mariel, Cuba</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CUMAR</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>253</v>
+      </c>
+      <c r="G252" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Manzanillo (Colima), Mexico</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>254</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Suape (Pernambuco), Brazil-Grand Cayman, Cayman Islands</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>KYGCM</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>255</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artifacts/input/destination_charges.xlsx
+++ b/artifacts/input/destination_charges.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:J267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,21 @@
           <t>SUAPE JOBS</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>porto de compara??o</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>GRANITO JOBS</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>GRANITO MARKUP USD</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7136,6 +7151,409 @@
       </c>
       <c r="G254" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Santo Tomas de Castilla, Guatemala</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-Santo Tomas de Castilla, Guatemala</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>256</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>GTSTC</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>1</v>
+      </c>
+      <c r="J255" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Santo Tomas de Castilla, Guatemala</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil-Santo Tomas de Castilla, Guatemala</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>257</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>GTSTC</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J256" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Altamira (Tamaulipas), Mexico</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-Altamira (Tamaulipas), Mexico</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>258</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>MXATM</t>
+        </is>
+      </c>
+      <c r="I257" t="n">
+        <v>1</v>
+      </c>
+      <c r="J257" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Veracruz (Veracruz Llave), Mexico</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-Veracruz (Veracruz Llave), Mexico</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>259</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>MXVCR</t>
+        </is>
+      </c>
+      <c r="I258" t="n">
+        <v>1</v>
+      </c>
+      <c r="J258" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Manzanillo, Panama</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-Manzanillo, Panama</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>260</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>1</v>
+      </c>
+      <c r="J259" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>261</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>DOCAU</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>1</v>
+      </c>
+      <c r="J260" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>262</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>PRSJU</t>
+        </is>
+      </c>
+      <c r="I261" t="n">
+        <v>1</v>
+      </c>
+      <c r="J261" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Cartagena (Bolivar), Colombia</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Vitoria (Espirito Santo), Brazil-Cartagena (Bolivar), Colombia</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>263</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>COCTG</t>
+        </is>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Veracruz (Veracruz Llave), Mexico</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil-Veracruz (Veracruz Llave), Mexico</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>264</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>MXVCR</t>
+        </is>
+      </c>
+      <c r="I263" t="n">
+        <v>1</v>
+      </c>
+      <c r="J263" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Manzanillo, Panama</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil-Manzanillo, Panama</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>265</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>PAMIT</t>
+        </is>
+      </c>
+      <c r="I264" t="n">
+        <v>1</v>
+      </c>
+      <c r="J264" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil-Caucedo, Dominican Republic</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>266</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>DOCAU</t>
+        </is>
+      </c>
+      <c r="I265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J265" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil-San Juan, Puerto Rico</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>267</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>PRSJU</t>
+        </is>
+      </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Cartagena (Bolivar), Colombia</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (Rio de Janeiro), Brazil-Cartagena (Bolivar), Colombia</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>268</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>COCTG</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>1</v>
+      </c>
+      <c r="J267" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
